--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="64">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>394.7</t>
+    <t>437.9</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.9</t>
+    <t>4.4</t>
   </si>
   <si>
     <t>01일</t>
@@ -101,25 +101,37 @@
     <t>05일</t>
   </si>
   <si>
-    <t>603.4</t>
-  </si>
-  <si>
-    <t>1973.3</t>
-  </si>
-  <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>19.7</t>
+    <t>649.0</t>
+  </si>
+  <si>
+    <t>2018.9</t>
+  </si>
+  <si>
+    <t>6.5</t>
+  </si>
+  <si>
+    <t>20.2</t>
   </si>
   <si>
     <t>06일</t>
   </si>
   <si>
+    <t>608.5</t>
+  </si>
+  <si>
+    <t>2627.4</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>26.3</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>07일</t>
   </si>
   <si>
     <t>08일</t>
@@ -605,13 +617,13 @@
         <v>34</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -619,19 +631,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -639,19 +651,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -659,19 +671,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -679,19 +691,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -699,19 +711,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -719,19 +731,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -739,19 +751,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -759,19 +771,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -779,19 +791,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -799,19 +811,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -819,19 +831,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -839,19 +851,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -859,19 +871,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -879,19 +891,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -899,19 +911,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -919,19 +931,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -939,19 +951,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -959,19 +971,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -979,19 +991,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -999,19 +1011,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1019,19 +1031,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1039,19 +1051,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1059,19 +1071,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1079,19 +1091,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1099,19 +1111,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="68">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>437.9</t>
+    <t>432.0</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.4</t>
+    <t>4.3</t>
   </si>
   <si>
     <t>01일</t>
@@ -131,10 +131,22 @@
     <t>07일</t>
   </si>
   <si>
+    <t>396.6</t>
+  </si>
+  <si>
+    <t>3024.0</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>30.2</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>08일</t>
   </si>
   <si>
     <t>09일</t>
@@ -637,13 +649,13 @@
         <v>39</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -651,19 +663,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -671,19 +683,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -691,19 +703,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -711,19 +723,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -731,19 +743,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -751,19 +763,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -771,19 +783,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -791,19 +803,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -811,19 +823,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -831,19 +843,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -851,19 +863,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -871,19 +883,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -891,19 +903,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -911,19 +923,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -931,19 +943,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -951,19 +963,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -971,19 +983,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -991,19 +1003,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1011,19 +1023,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1031,19 +1043,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1051,19 +1063,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1071,19 +1083,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1091,19 +1103,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1111,19 +1123,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="72">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>432.0</t>
+    <t>453.2</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.3</t>
+    <t>4.5</t>
   </si>
   <si>
     <t>01일</t>
@@ -146,10 +146,22 @@
     <t>08일</t>
   </si>
   <si>
+    <t>601.7</t>
+  </si>
+  <si>
+    <t>3625.7</t>
+  </si>
+  <si>
+    <t>6.0</t>
+  </si>
+  <si>
+    <t>36.3</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>09일</t>
   </si>
   <si>
     <t>10일</t>
@@ -669,13 +681,13 @@
         <v>44</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -683,19 +695,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -703,19 +715,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -723,19 +735,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -743,19 +755,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -763,19 +775,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -783,19 +795,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -803,19 +815,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -823,19 +835,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -843,19 +855,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -863,19 +875,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -883,19 +895,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -903,19 +915,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -923,19 +935,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -943,19 +955,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -963,19 +975,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -983,19 +995,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1003,19 +1015,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1023,19 +1035,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1043,19 +1055,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1063,19 +1075,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1083,19 +1095,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1103,19 +1115,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1123,19 +1135,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="75">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>453.2</t>
+    <t>472.7</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.5</t>
+    <t>4.7</t>
   </si>
   <si>
     <t>01일</t>
@@ -146,10 +146,10 @@
     <t>08일</t>
   </si>
   <si>
-    <t>601.7</t>
-  </si>
-  <si>
-    <t>3625.7</t>
+    <t>602.0</t>
+  </si>
+  <si>
+    <t>3626.0</t>
   </si>
   <si>
     <t>6.0</t>
@@ -161,10 +161,19 @@
     <t>09일</t>
   </si>
   <si>
+    <t>628.3</t>
+  </si>
+  <si>
+    <t>4254.3</t>
+  </si>
+  <si>
+    <t>42.5</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>10일</t>
   </si>
   <si>
     <t>11일</t>
@@ -701,13 +710,13 @@
         <v>49</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -715,19 +724,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -735,19 +744,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -755,19 +764,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -775,19 +784,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -795,19 +804,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -815,19 +824,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -835,19 +844,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -855,19 +864,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -875,19 +884,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -895,19 +904,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -915,19 +924,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -935,19 +944,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -955,19 +964,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -975,19 +984,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -995,19 +1004,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1015,19 +1024,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1035,19 +1044,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1055,19 +1064,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1075,19 +1084,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1095,19 +1104,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1115,19 +1124,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1135,19 +1144,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="79">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>472.7</t>
+    <t>484.8</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.7</t>
+    <t>4.8</t>
   </si>
   <si>
     <t>01일</t>
@@ -161,10 +161,10 @@
     <t>09일</t>
   </si>
   <si>
-    <t>628.3</t>
-  </si>
-  <si>
-    <t>4254.3</t>
+    <t>628.9</t>
+  </si>
+  <si>
+    <t>4254.9</t>
   </si>
   <si>
     <t>42.5</t>
@@ -173,10 +173,22 @@
     <t>10일</t>
   </si>
   <si>
+    <t>593.4</t>
+  </si>
+  <si>
+    <t>4848.3</t>
+  </si>
+  <si>
+    <t>5.9</t>
+  </si>
+  <si>
+    <t>48.5</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>11일</t>
   </si>
   <si>
     <t>12일</t>
@@ -730,13 +742,13 @@
         <v>53</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -744,19 +756,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -764,19 +776,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -784,19 +796,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -804,19 +816,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -824,19 +836,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -844,19 +856,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -864,19 +876,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -884,19 +896,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -904,19 +916,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -924,19 +936,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -944,19 +956,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -964,19 +976,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -984,19 +996,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1004,19 +1016,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1024,19 +1036,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1044,19 +1056,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1064,19 +1076,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1084,19 +1096,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1104,19 +1116,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1124,19 +1136,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1144,19 +1156,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="83">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>484.8</t>
+    <t>464.8</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.8</t>
+    <t>4.6</t>
   </si>
   <si>
     <t>01일</t>
@@ -173,10 +173,10 @@
     <t>10일</t>
   </si>
   <si>
-    <t>593.4</t>
-  </si>
-  <si>
-    <t>4848.3</t>
+    <t>593.9</t>
+  </si>
+  <si>
+    <t>4848.8</t>
   </si>
   <si>
     <t>5.9</t>
@@ -188,10 +188,22 @@
     <t>11일</t>
   </si>
   <si>
+    <t>264.2</t>
+  </si>
+  <si>
+    <t>5113.0</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>51.1</t>
+  </si>
+  <si>
+    <t>12일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>12일</t>
   </si>
   <si>
     <t>13일</t>
@@ -762,13 +774,13 @@
         <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -776,19 +788,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -796,19 +808,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -816,19 +828,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -836,19 +848,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -856,19 +868,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -876,19 +888,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -896,19 +908,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -916,19 +928,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -936,19 +948,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -956,19 +968,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -976,19 +988,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -996,19 +1008,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1016,19 +1028,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1036,19 +1048,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1056,19 +1068,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1076,19 +1088,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1096,19 +1108,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1116,19 +1128,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1136,19 +1148,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1156,19 +1168,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="87">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>464.8</t>
+    <t>467.3</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.6</t>
+    <t>4.7</t>
   </si>
   <si>
     <t>01일</t>
@@ -203,10 +203,22 @@
     <t>12일</t>
   </si>
   <si>
+    <t>494.2</t>
+  </si>
+  <si>
+    <t>5607.2</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>56.1</t>
+  </si>
+  <si>
+    <t>13일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>13일</t>
   </si>
   <si>
     <t>14일</t>
@@ -794,13 +806,13 @@
         <v>63</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -808,19 +820,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -828,19 +840,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -848,19 +860,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -868,19 +880,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -888,19 +900,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -908,19 +920,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -928,19 +940,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -948,19 +960,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -968,19 +980,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -988,19 +1000,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1008,19 +1020,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1028,19 +1040,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1048,19 +1060,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1068,19 +1080,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1088,19 +1100,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1108,19 +1120,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1128,19 +1140,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1148,19 +1160,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1168,19 +1180,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="90">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>467.3</t>
+    <t>477.8</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.7</t>
+    <t>4.8</t>
   </si>
   <si>
     <t>01일</t>
@@ -218,10 +218,19 @@
     <t>13일</t>
   </si>
   <si>
+    <t>603.8</t>
+  </si>
+  <si>
+    <t>6211.0</t>
+  </si>
+  <si>
+    <t>62.1</t>
+  </si>
+  <si>
+    <t>14일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>14일</t>
   </si>
   <si>
     <t>15일</t>
@@ -826,13 +835,13 @@
         <v>68</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -840,19 +849,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -860,19 +869,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -880,19 +889,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -900,19 +909,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -920,19 +929,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -940,19 +949,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -960,19 +969,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -980,19 +989,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1000,19 +1009,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1020,19 +1029,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1040,19 +1049,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1060,19 +1069,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1080,19 +1089,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1100,19 +1109,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1120,19 +1129,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1140,19 +1149,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1160,19 +1169,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1180,19 +1189,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>477.8</t>
+    <t>485.9</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.8</t>
+    <t>4.9</t>
   </si>
   <si>
     <t>01일</t>
@@ -209,9 +209,6 @@
     <t>5607.2</t>
   </si>
   <si>
-    <t>4.9</t>
-  </si>
-  <si>
     <t>56.1</t>
   </si>
   <si>
@@ -230,10 +227,19 @@
     <t>14일</t>
   </si>
   <si>
+    <t>592.3</t>
+  </si>
+  <si>
+    <t>6803.3</t>
+  </si>
+  <si>
+    <t>68.0</t>
+  </si>
+  <si>
+    <t>15일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>15일</t>
   </si>
   <si>
     <t>16일</t>
@@ -818,10 +824,10 @@
         <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s" s="39">
         <v>65</v>
-      </c>
-      <c r="F14" t="s" s="39">
-        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -829,19 +835,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
+        <v>66</v>
+      </c>
+      <c r="C15" t="s" s="31">
         <v>67</v>
       </c>
-      <c r="C15" t="s" s="31">
+      <c r="D15" t="s" s="32">
         <v>68</v>
-      </c>
-      <c r="D15" t="s" s="32">
-        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
         <v>46</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -849,19 +855,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s" s="36">
         <v>71</v>
-      </c>
-      <c r="C16" t="s" s="36">
-        <v>72</v>
       </c>
       <c r="D16" t="s" s="37">
         <v>72</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -869,19 +875,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -889,19 +895,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -909,19 +915,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -929,19 +935,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -949,19 +955,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -969,19 +975,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -989,19 +995,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1009,19 +1015,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1029,19 +1035,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1049,19 +1055,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1069,19 +1075,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1089,19 +1095,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1109,19 +1115,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1129,19 +1135,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1149,19 +1155,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1169,19 +1175,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1189,19 +1195,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="95">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>485.9</t>
+    <t>493.5</t>
   </si>
   <si>
     <t>-</t>
@@ -239,10 +239,19 @@
     <t>15일</t>
   </si>
   <si>
+    <t>599.1</t>
+  </si>
+  <si>
+    <t>7402.4</t>
+  </si>
+  <si>
+    <t>74.0</t>
+  </si>
+  <si>
+    <t>16일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>16일</t>
   </si>
   <si>
     <t>17일</t>
@@ -881,13 +890,13 @@
         <v>75</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -895,19 +904,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -915,19 +924,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -935,19 +944,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -955,19 +964,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -975,19 +984,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -995,19 +1004,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1015,19 +1024,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1035,19 +1044,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1055,19 +1064,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1075,19 +1084,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1095,19 +1104,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1115,19 +1124,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1135,19 +1144,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1155,19 +1164,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1175,19 +1184,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1195,19 +1204,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="99">
   <si>
     <t>No.</t>
   </si>
@@ -35,180 +35,183 @@
     <t>평균</t>
   </si>
   <si>
-    <t>493.5</t>
+    <t>499.7</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>275.8</t>
+  </si>
+  <si>
+    <t>2.8</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>353.8</t>
+  </si>
+  <si>
+    <t>629.6</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>103.9</t>
+  </si>
+  <si>
+    <t>733.5</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>7.3</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>636.4</t>
+  </si>
+  <si>
+    <t>1369.9</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>13.7</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>649.0</t>
+  </si>
+  <si>
+    <t>2018.9</t>
+  </si>
+  <si>
+    <t>6.5</t>
+  </si>
+  <si>
+    <t>20.2</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>608.5</t>
+  </si>
+  <si>
+    <t>2627.4</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>26.3</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>396.6</t>
+  </si>
+  <si>
+    <t>3024.0</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>30.2</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>602.0</t>
+  </si>
+  <si>
+    <t>3626.0</t>
+  </si>
+  <si>
+    <t>6.0</t>
+  </si>
+  <si>
+    <t>36.3</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>628.9</t>
+  </si>
+  <si>
+    <t>4254.9</t>
+  </si>
+  <si>
+    <t>42.5</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
+    <t>593.9</t>
+  </si>
+  <si>
+    <t>4848.8</t>
+  </si>
+  <si>
+    <t>5.9</t>
+  </si>
+  <si>
+    <t>48.5</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
+    <t>264.2</t>
+  </si>
+  <si>
+    <t>5113.0</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>51.1</t>
+  </si>
+  <si>
+    <t>12일</t>
+  </si>
+  <si>
+    <t>494.2</t>
+  </si>
+  <si>
+    <t>5607.2</t>
+  </si>
+  <si>
     <t>4.9</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>275.8</t>
-  </si>
-  <si>
-    <t>2.8</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>353.8</t>
-  </si>
-  <si>
-    <t>629.6</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>6.3</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>103.9</t>
-  </si>
-  <si>
-    <t>733.5</t>
-  </si>
-  <si>
-    <t>1.0</t>
-  </si>
-  <si>
-    <t>7.3</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>636.4</t>
-  </si>
-  <si>
-    <t>1369.9</t>
-  </si>
-  <si>
-    <t>6.4</t>
-  </si>
-  <si>
-    <t>13.7</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>649.0</t>
-  </si>
-  <si>
-    <t>2018.9</t>
-  </si>
-  <si>
-    <t>6.5</t>
-  </si>
-  <si>
-    <t>20.2</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>608.5</t>
-  </si>
-  <si>
-    <t>2627.4</t>
-  </si>
-  <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>26.3</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>396.6</t>
-  </si>
-  <si>
-    <t>3024.0</t>
-  </si>
-  <si>
-    <t>4.0</t>
-  </si>
-  <si>
-    <t>30.2</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>602.0</t>
-  </si>
-  <si>
-    <t>3626.0</t>
-  </si>
-  <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>36.3</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>628.9</t>
-  </si>
-  <si>
-    <t>4254.9</t>
-  </si>
-  <si>
-    <t>42.5</t>
-  </si>
-  <si>
-    <t>10일</t>
-  </si>
-  <si>
-    <t>593.9</t>
-  </si>
-  <si>
-    <t>4848.8</t>
-  </si>
-  <si>
-    <t>5.9</t>
-  </si>
-  <si>
-    <t>48.5</t>
-  </si>
-  <si>
-    <t>11일</t>
-  </si>
-  <si>
-    <t>264.2</t>
-  </si>
-  <si>
-    <t>5113.0</t>
-  </si>
-  <si>
-    <t>2.6</t>
-  </si>
-  <si>
-    <t>51.1</t>
-  </si>
-  <si>
-    <t>12일</t>
-  </si>
-  <si>
-    <t>494.2</t>
-  </si>
-  <si>
-    <t>5607.2</t>
-  </si>
-  <si>
     <t>56.1</t>
   </si>
   <si>
@@ -251,10 +254,19 @@
     <t>16일</t>
   </si>
   <si>
+    <t>593.5</t>
+  </si>
+  <si>
+    <t>7995.9</t>
+  </si>
+  <si>
+    <t>80.0</t>
+  </si>
+  <si>
+    <t>17일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>17일</t>
   </si>
   <si>
     <t>18일</t>
@@ -833,10 +845,10 @@
         <v>64</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -844,19 +856,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="33">
         <v>46</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -864,19 +876,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s" s="38">
         <v>55</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -884,19 +896,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s" s="33">
         <v>46</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -904,19 +916,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -924,19 +936,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -944,19 +956,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -964,19 +976,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -984,19 +996,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1004,19 +1016,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1024,19 +1036,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1044,19 +1056,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1064,19 +1076,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1084,19 +1096,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1104,19 +1116,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1124,19 +1136,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1144,19 +1156,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1164,19 +1176,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1184,19 +1196,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1204,19 +1216,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="103">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>499.7</t>
+    <t>504.8</t>
   </si>
   <si>
     <t>-</t>
@@ -254,10 +254,10 @@
     <t>16일</t>
   </si>
   <si>
-    <t>593.5</t>
-  </si>
-  <si>
-    <t>7995.9</t>
+    <t>594.3</t>
+  </si>
+  <si>
+    <t>7996.7</t>
   </si>
   <si>
     <t>80.0</t>
@@ -266,10 +266,22 @@
     <t>17일</t>
   </si>
   <si>
+    <t>584.5</t>
+  </si>
+  <si>
+    <t>8581.2</t>
+  </si>
+  <si>
+    <t>5.8</t>
+  </si>
+  <si>
+    <t>85.8</t>
+  </si>
+  <si>
+    <t>18일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>18일</t>
   </si>
   <si>
     <t>19일</t>
@@ -942,13 +954,13 @@
         <v>84</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -956,19 +968,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -976,19 +988,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -996,19 +1008,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1016,19 +1028,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1036,19 +1048,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1056,19 +1068,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1076,19 +1088,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1096,19 +1108,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1116,19 +1128,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1136,19 +1148,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1156,19 +1168,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1176,19 +1188,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1196,19 +1208,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1216,19 +1228,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="106">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>504.8</t>
+    <t>509.1</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>5.0</t>
+    <t>5.1</t>
   </si>
   <si>
     <t>01일</t>
@@ -266,10 +266,10 @@
     <t>17일</t>
   </si>
   <si>
-    <t>584.5</t>
-  </si>
-  <si>
-    <t>8581.2</t>
+    <t>584.9</t>
+  </si>
+  <si>
+    <t>8581.6</t>
   </si>
   <si>
     <t>5.8</t>
@@ -281,10 +281,19 @@
     <t>18일</t>
   </si>
   <si>
+    <t>582.1</t>
+  </si>
+  <si>
+    <t>9163.7</t>
+  </si>
+  <si>
+    <t>91.6</t>
+  </si>
+  <si>
+    <t>19일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>19일</t>
   </si>
   <si>
     <t>20일</t>
@@ -974,13 +983,13 @@
         <v>89</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -988,19 +997,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1008,19 +1017,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1028,19 +1037,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1048,19 +1057,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1068,19 +1077,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1088,19 +1097,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1108,19 +1117,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1128,19 +1137,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1148,19 +1157,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1168,19 +1177,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1188,19 +1197,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1208,19 +1217,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1228,19 +1237,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="110">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>509.1</t>
+    <t>500.3</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>5.1</t>
+    <t>5.0</t>
   </si>
   <si>
     <t>01일</t>
@@ -293,10 +293,22 @@
     <t>19일</t>
   </si>
   <si>
+    <t>342.7</t>
+  </si>
+  <si>
+    <t>9506.4</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>95.1</t>
+  </si>
+  <si>
+    <t>20일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>20일</t>
   </si>
   <si>
     <t>21일</t>
@@ -1003,13 +1015,13 @@
         <v>93</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1017,19 +1029,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1037,19 +1049,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1057,19 +1069,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1077,19 +1089,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1097,19 +1109,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1117,19 +1129,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1137,19 +1149,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1157,19 +1169,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1177,19 +1189,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1197,19 +1209,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1217,19 +1229,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1237,19 +1249,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="114">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>500.3</t>
+    <t>478.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>5.0</t>
+    <t>4.8</t>
   </si>
   <si>
     <t>01일</t>
@@ -308,10 +308,22 @@
     <t>20일</t>
   </si>
   <si>
+    <t>66.3</t>
+  </si>
+  <si>
+    <t>9572.7</t>
+  </si>
+  <si>
+    <t>0.7</t>
+  </si>
+  <si>
+    <t>95.7</t>
+  </si>
+  <si>
+    <t>21일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>21일</t>
   </si>
   <si>
     <t>22일</t>
@@ -1035,13 +1047,13 @@
         <v>98</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1049,19 +1061,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1069,19 +1081,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1089,19 +1101,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1109,19 +1121,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1129,19 +1141,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1149,19 +1161,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1169,19 +1181,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1189,19 +1201,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1209,19 +1221,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1229,19 +1241,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1249,19 +1261,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="118">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>478.6</t>
+    <t>462.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.8</t>
+    <t>4.6</t>
   </si>
   <si>
     <t>01일</t>
@@ -323,10 +323,22 @@
     <t>21일</t>
   </si>
   <si>
+    <t>141.4</t>
+  </si>
+  <si>
+    <t>9714.1</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>97.1</t>
+  </si>
+  <si>
+    <t>22일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>22일</t>
   </si>
   <si>
     <t>23일</t>
@@ -1067,13 +1079,13 @@
         <v>103</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1081,19 +1093,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1101,19 +1113,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1121,19 +1133,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1141,19 +1153,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1161,19 +1173,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1181,19 +1193,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1201,19 +1213,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1221,19 +1233,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1241,19 +1253,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1261,19 +1273,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="121">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>462.6</t>
+    <t>469.1</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.6</t>
+    <t>4.7</t>
   </si>
   <si>
     <t>01일</t>
@@ -338,10 +338,19 @@
     <t>22일</t>
   </si>
   <si>
+    <t>606.3</t>
+  </si>
+  <si>
+    <t>10320.4</t>
+  </si>
+  <si>
+    <t>103.2</t>
+  </si>
+  <si>
+    <t>23일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>23일</t>
   </si>
   <si>
     <t>24일</t>
@@ -1099,13 +1108,13 @@
         <v>108</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>108</v>
+        <v>36</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1113,19 +1122,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1133,19 +1142,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1153,19 +1162,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1173,19 +1182,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1193,19 +1202,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1213,19 +1222,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1233,19 +1242,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1253,19 +1262,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1273,19 +1282,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="124">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>469.1</t>
+    <t>468.9</t>
   </si>
   <si>
     <t>-</t>
@@ -350,10 +350,19 @@
     <t>23일</t>
   </si>
   <si>
+    <t>465.3</t>
+  </si>
+  <si>
+    <t>10785.7</t>
+  </si>
+  <si>
+    <t>107.9</t>
+  </si>
+  <si>
+    <t>24일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>24일</t>
   </si>
   <si>
     <t>25일</t>
@@ -1128,13 +1137,13 @@
         <v>112</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1142,19 +1151,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1162,19 +1171,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1182,19 +1191,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1202,19 +1211,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1222,19 +1231,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1242,19 +1251,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1262,19 +1271,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1282,19 +1291,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="127">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>468.9</t>
+    <t>474.5</t>
   </si>
   <si>
     <t>-</t>
@@ -350,10 +350,10 @@
     <t>23일</t>
   </si>
   <si>
-    <t>465.3</t>
-  </si>
-  <si>
-    <t>10785.7</t>
+    <t>465.6</t>
+  </si>
+  <si>
+    <t>10786.0</t>
   </si>
   <si>
     <t>107.9</t>
@@ -362,10 +362,19 @@
     <t>24일</t>
   </si>
   <si>
+    <t>601.4</t>
+  </si>
+  <si>
+    <t>11387.4</t>
+  </si>
+  <si>
+    <t>113.9</t>
+  </si>
+  <si>
+    <t>25일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>25일</t>
   </si>
   <si>
     <t>26일</t>
@@ -1157,13 +1166,13 @@
         <v>116</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1171,19 +1180,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1191,19 +1200,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1211,19 +1220,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1231,19 +1240,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1251,19 +1260,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1271,19 +1280,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1291,19 +1300,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="132">
   <si>
     <t>No.</t>
   </si>
@@ -35,327 +35,330 @@
     <t>평균</t>
   </si>
   <si>
-    <t>474.5</t>
+    <t>476.8</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>275.8</t>
+  </si>
+  <si>
+    <t>2.8</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>353.8</t>
+  </si>
+  <si>
+    <t>629.6</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>103.9</t>
+  </si>
+  <si>
+    <t>733.5</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>7.3</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>636.4</t>
+  </si>
+  <si>
+    <t>1369.9</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>13.7</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>649.0</t>
+  </si>
+  <si>
+    <t>2018.9</t>
+  </si>
+  <si>
+    <t>6.5</t>
+  </si>
+  <si>
+    <t>20.2</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>608.5</t>
+  </si>
+  <si>
+    <t>2627.4</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>26.3</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>396.6</t>
+  </si>
+  <si>
+    <t>3024.0</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>30.2</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>602.0</t>
+  </si>
+  <si>
+    <t>3626.0</t>
+  </si>
+  <si>
+    <t>6.0</t>
+  </si>
+  <si>
+    <t>36.3</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>628.9</t>
+  </si>
+  <si>
+    <t>4254.9</t>
+  </si>
+  <si>
+    <t>42.5</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
+    <t>593.9</t>
+  </si>
+  <si>
+    <t>4848.8</t>
+  </si>
+  <si>
+    <t>5.9</t>
+  </si>
+  <si>
+    <t>48.5</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
+    <t>264.2</t>
+  </si>
+  <si>
+    <t>5113.0</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>51.1</t>
+  </si>
+  <si>
+    <t>12일</t>
+  </si>
+  <si>
+    <t>494.2</t>
+  </si>
+  <si>
+    <t>5607.2</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>56.1</t>
+  </si>
+  <si>
+    <t>13일</t>
+  </si>
+  <si>
+    <t>603.8</t>
+  </si>
+  <si>
+    <t>6211.0</t>
+  </si>
+  <si>
+    <t>62.1</t>
+  </si>
+  <si>
+    <t>14일</t>
+  </si>
+  <si>
+    <t>592.3</t>
+  </si>
+  <si>
+    <t>6803.3</t>
+  </si>
+  <si>
+    <t>68.0</t>
+  </si>
+  <si>
+    <t>15일</t>
+  </si>
+  <si>
+    <t>599.1</t>
+  </si>
+  <si>
+    <t>7402.4</t>
+  </si>
+  <si>
+    <t>74.0</t>
+  </si>
+  <si>
+    <t>16일</t>
+  </si>
+  <si>
+    <t>594.3</t>
+  </si>
+  <si>
+    <t>7996.7</t>
+  </si>
+  <si>
+    <t>80.0</t>
+  </si>
+  <si>
+    <t>17일</t>
+  </si>
+  <si>
+    <t>584.9</t>
+  </si>
+  <si>
+    <t>8581.6</t>
+  </si>
+  <si>
+    <t>5.8</t>
+  </si>
+  <si>
+    <t>85.8</t>
+  </si>
+  <si>
+    <t>18일</t>
+  </si>
+  <si>
+    <t>582.1</t>
+  </si>
+  <si>
+    <t>9163.7</t>
+  </si>
+  <si>
+    <t>91.6</t>
+  </si>
+  <si>
+    <t>19일</t>
+  </si>
+  <si>
+    <t>342.7</t>
+  </si>
+  <si>
+    <t>9506.4</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>95.1</t>
+  </si>
+  <si>
+    <t>20일</t>
+  </si>
+  <si>
+    <t>66.3</t>
+  </si>
+  <si>
+    <t>9572.7</t>
+  </si>
+  <si>
+    <t>0.7</t>
+  </si>
+  <si>
+    <t>95.7</t>
+  </si>
+  <si>
+    <t>21일</t>
+  </si>
+  <si>
+    <t>141.4</t>
+  </si>
+  <si>
+    <t>9714.1</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>97.1</t>
+  </si>
+  <si>
+    <t>22일</t>
+  </si>
+  <si>
+    <t>606.3</t>
+  </si>
+  <si>
+    <t>10320.4</t>
+  </si>
+  <si>
+    <t>103.2</t>
+  </si>
+  <si>
+    <t>23일</t>
+  </si>
+  <si>
+    <t>465.6</t>
+  </si>
+  <si>
+    <t>10786.0</t>
+  </si>
+  <si>
     <t>4.7</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>275.8</t>
-  </si>
-  <si>
-    <t>2.8</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>353.8</t>
-  </si>
-  <si>
-    <t>629.6</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>6.3</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>103.9</t>
-  </si>
-  <si>
-    <t>733.5</t>
-  </si>
-  <si>
-    <t>1.0</t>
-  </si>
-  <si>
-    <t>7.3</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>636.4</t>
-  </si>
-  <si>
-    <t>1369.9</t>
-  </si>
-  <si>
-    <t>6.4</t>
-  </si>
-  <si>
-    <t>13.7</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>649.0</t>
-  </si>
-  <si>
-    <t>2018.9</t>
-  </si>
-  <si>
-    <t>6.5</t>
-  </si>
-  <si>
-    <t>20.2</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>608.5</t>
-  </si>
-  <si>
-    <t>2627.4</t>
-  </si>
-  <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>26.3</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>396.6</t>
-  </si>
-  <si>
-    <t>3024.0</t>
-  </si>
-  <si>
-    <t>4.0</t>
-  </si>
-  <si>
-    <t>30.2</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>602.0</t>
-  </si>
-  <si>
-    <t>3626.0</t>
-  </si>
-  <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>36.3</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>628.9</t>
-  </si>
-  <si>
-    <t>4254.9</t>
-  </si>
-  <si>
-    <t>42.5</t>
-  </si>
-  <si>
-    <t>10일</t>
-  </si>
-  <si>
-    <t>593.9</t>
-  </si>
-  <si>
-    <t>4848.8</t>
-  </si>
-  <si>
-    <t>5.9</t>
-  </si>
-  <si>
-    <t>48.5</t>
-  </si>
-  <si>
-    <t>11일</t>
-  </si>
-  <si>
-    <t>264.2</t>
-  </si>
-  <si>
-    <t>5113.0</t>
-  </si>
-  <si>
-    <t>2.6</t>
-  </si>
-  <si>
-    <t>51.1</t>
-  </si>
-  <si>
-    <t>12일</t>
-  </si>
-  <si>
-    <t>494.2</t>
-  </si>
-  <si>
-    <t>5607.2</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>56.1</t>
-  </si>
-  <si>
-    <t>13일</t>
-  </si>
-  <si>
-    <t>603.8</t>
-  </si>
-  <si>
-    <t>6211.0</t>
-  </si>
-  <si>
-    <t>62.1</t>
-  </si>
-  <si>
-    <t>14일</t>
-  </si>
-  <si>
-    <t>592.3</t>
-  </si>
-  <si>
-    <t>6803.3</t>
-  </si>
-  <si>
-    <t>68.0</t>
-  </si>
-  <si>
-    <t>15일</t>
-  </si>
-  <si>
-    <t>599.1</t>
-  </si>
-  <si>
-    <t>7402.4</t>
-  </si>
-  <si>
-    <t>74.0</t>
-  </si>
-  <si>
-    <t>16일</t>
-  </si>
-  <si>
-    <t>594.3</t>
-  </si>
-  <si>
-    <t>7996.7</t>
-  </si>
-  <si>
-    <t>80.0</t>
-  </si>
-  <si>
-    <t>17일</t>
-  </si>
-  <si>
-    <t>584.9</t>
-  </si>
-  <si>
-    <t>8581.6</t>
-  </si>
-  <si>
-    <t>5.8</t>
-  </si>
-  <si>
-    <t>85.8</t>
-  </si>
-  <si>
-    <t>18일</t>
-  </si>
-  <si>
-    <t>582.1</t>
-  </si>
-  <si>
-    <t>9163.7</t>
-  </si>
-  <si>
-    <t>91.6</t>
-  </si>
-  <si>
-    <t>19일</t>
-  </si>
-  <si>
-    <t>342.7</t>
-  </si>
-  <si>
-    <t>9506.4</t>
-  </si>
-  <si>
-    <t>3.4</t>
-  </si>
-  <si>
-    <t>95.1</t>
-  </si>
-  <si>
-    <t>20일</t>
-  </si>
-  <si>
-    <t>66.3</t>
-  </si>
-  <si>
-    <t>9572.7</t>
-  </si>
-  <si>
-    <t>0.7</t>
-  </si>
-  <si>
-    <t>95.7</t>
-  </si>
-  <si>
-    <t>21일</t>
-  </si>
-  <si>
-    <t>141.4</t>
-  </si>
-  <si>
-    <t>9714.1</t>
-  </si>
-  <si>
-    <t>1.4</t>
-  </si>
-  <si>
-    <t>97.1</t>
-  </si>
-  <si>
-    <t>22일</t>
-  </si>
-  <si>
-    <t>606.3</t>
-  </si>
-  <si>
-    <t>10320.4</t>
-  </si>
-  <si>
-    <t>103.2</t>
-  </si>
-  <si>
-    <t>23일</t>
-  </si>
-  <si>
-    <t>465.6</t>
-  </si>
-  <si>
-    <t>10786.0</t>
-  </si>
-  <si>
     <t>107.9</t>
   </si>
   <si>
@@ -374,10 +377,22 @@
     <t>25일</t>
   </si>
   <si>
+    <t>532.4</t>
+  </si>
+  <si>
+    <t>11919.8</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>119.2</t>
+  </si>
+  <si>
+    <t>26일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>26일</t>
   </si>
   <si>
     <t>27일</t>
@@ -1149,10 +1164,10 @@
         <v>113</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>9</v>
+        <v>114</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1160,19 +1175,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E26" t="s" s="38">
         <v>46</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1180,19 +1195,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1200,19 +1215,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1220,19 +1235,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1240,19 +1255,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1260,19 +1275,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1280,19 +1295,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1300,19 +1315,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="140">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>476.8</t>
+    <t>464.7</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.8</t>
+    <t>4.6</t>
   </si>
   <si>
     <t>01일</t>
@@ -392,13 +392,37 @@
     <t>26일</t>
   </si>
   <si>
+    <t>448.2</t>
+  </si>
+  <si>
+    <t>12368.0</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>123.7</t>
+  </si>
+  <si>
+    <t>27일</t>
+  </si>
+  <si>
+    <t>179.0</t>
+  </si>
+  <si>
+    <t>12547.0</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>125.5</t>
+  </si>
+  <si>
+    <t>28일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>27일</t>
-  </si>
-  <si>
-    <t>28일</t>
   </si>
   <si>
     <t>29일</t>
@@ -1221,13 +1245,13 @@
         <v>126</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1235,19 +1259,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1255,19 +1279,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1275,19 +1299,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1295,19 +1319,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1315,19 +1339,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="144">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>464.7</t>
+    <t>459.1</t>
   </si>
   <si>
     <t>-</t>
@@ -422,10 +422,22 @@
     <t>28일</t>
   </si>
   <si>
+    <t>307.4</t>
+  </si>
+  <si>
+    <t>12854.4</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>128.5</t>
+  </si>
+  <si>
+    <t>29일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>29일</t>
   </si>
   <si>
     <t>30일</t>
@@ -1285,13 +1297,13 @@
         <v>136</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1299,19 +1311,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1319,19 +1331,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1339,19 +1351,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="147">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>459.1</t>
+    <t>463.2</t>
   </si>
   <si>
     <t>-</t>
@@ -437,10 +437,19 @@
     <t>29일</t>
   </si>
   <si>
+    <t>578.2</t>
+  </si>
+  <si>
+    <t>13432.6</t>
+  </si>
+  <si>
+    <t>134.3</t>
+  </si>
+  <si>
+    <t>30일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>30일</t>
   </si>
   <si>
     <t>31일</t>
@@ -1317,13 +1326,13 @@
         <v>141</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>141</v>
+        <v>86</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1331,19 +1340,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1351,19 +1360,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="149">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>463.2</t>
+    <t>467.4</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.6</t>
+    <t>4.7</t>
   </si>
   <si>
     <t>01일</t>
@@ -356,9 +356,6 @@
     <t>10786.0</t>
   </si>
   <si>
-    <t>4.7</t>
-  </si>
-  <si>
     <t>107.9</t>
   </si>
   <si>
@@ -449,10 +446,19 @@
     <t>30일</t>
   </si>
   <si>
+    <t>590.4</t>
+  </si>
+  <si>
+    <t>14023.0</t>
+  </si>
+  <si>
+    <t>140.2</t>
+  </si>
+  <si>
+    <t>31일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>31일</t>
   </si>
 </sst>
 </file>
@@ -1209,10 +1215,10 @@
         <v>113</v>
       </c>
       <c r="E25" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s" s="34">
         <v>114</v>
-      </c>
-      <c r="F25" t="s" s="34">
-        <v>115</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1220,19 +1226,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
+        <v>115</v>
+      </c>
+      <c r="C26" t="s" s="36">
         <v>116</v>
       </c>
-      <c r="C26" t="s" s="36">
+      <c r="D26" t="s" s="37">
         <v>117</v>
-      </c>
-      <c r="D26" t="s" s="37">
-        <v>118</v>
       </c>
       <c r="E26" t="s" s="38">
         <v>46</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1240,19 +1246,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
+        <v>119</v>
+      </c>
+      <c r="C27" t="s" s="31">
         <v>120</v>
       </c>
-      <c r="C27" t="s" s="31">
+      <c r="D27" t="s" s="32">
         <v>121</v>
       </c>
-      <c r="D27" t="s" s="32">
+      <c r="E27" t="s" s="33">
         <v>122</v>
       </c>
-      <c r="E27" t="s" s="33">
+      <c r="F27" t="s" s="34">
         <v>123</v>
-      </c>
-      <c r="F27" t="s" s="34">
-        <v>124</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1260,19 +1266,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
+        <v>124</v>
+      </c>
+      <c r="C28" t="s" s="36">
         <v>125</v>
       </c>
-      <c r="C28" t="s" s="36">
+      <c r="D28" t="s" s="37">
         <v>126</v>
       </c>
-      <c r="D28" t="s" s="37">
+      <c r="E28" t="s" s="38">
         <v>127</v>
       </c>
-      <c r="E28" t="s" s="38">
+      <c r="F28" t="s" s="39">
         <v>128</v>
-      </c>
-      <c r="F28" t="s" s="39">
-        <v>129</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1280,19 +1286,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
+        <v>129</v>
+      </c>
+      <c r="C29" t="s" s="31">
         <v>130</v>
       </c>
-      <c r="C29" t="s" s="31">
+      <c r="D29" t="s" s="32">
         <v>131</v>
       </c>
-      <c r="D29" t="s" s="32">
+      <c r="E29" t="s" s="33">
         <v>132</v>
       </c>
-      <c r="E29" t="s" s="33">
+      <c r="F29" t="s" s="34">
         <v>133</v>
-      </c>
-      <c r="F29" t="s" s="34">
-        <v>134</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1300,19 +1306,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
+        <v>134</v>
+      </c>
+      <c r="C30" t="s" s="36">
         <v>135</v>
       </c>
-      <c r="C30" t="s" s="36">
+      <c r="D30" t="s" s="37">
         <v>136</v>
       </c>
-      <c r="D30" t="s" s="37">
+      <c r="E30" t="s" s="38">
         <v>137</v>
       </c>
-      <c r="E30" t="s" s="38">
+      <c r="F30" t="s" s="39">
         <v>138</v>
-      </c>
-      <c r="F30" t="s" s="39">
-        <v>139</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1320,19 +1326,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
+        <v>139</v>
+      </c>
+      <c r="C31" t="s" s="31">
         <v>140</v>
       </c>
-      <c r="C31" t="s" s="31">
+      <c r="D31" t="s" s="32">
         <v>141</v>
-      </c>
-      <c r="D31" t="s" s="32">
-        <v>142</v>
       </c>
       <c r="E31" t="s" s="33">
         <v>86</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1340,19 +1346,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
+        <v>143</v>
+      </c>
+      <c r="C32" t="s" s="36">
         <v>144</v>
-      </c>
-      <c r="C32" t="s" s="36">
-        <v>145</v>
       </c>
       <c r="D32" t="s" s="37">
         <v>145</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1360,19 +1366,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-05-01.xlsx
+++ b/past_data/site_8024/2026-05-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="151">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>467.4</t>
+    <t>471.0</t>
   </si>
   <si>
     <t>-</t>
@@ -446,10 +446,10 @@
     <t>30일</t>
   </si>
   <si>
-    <t>590.4</t>
-  </si>
-  <si>
-    <t>14023.0</t>
+    <t>590.6</t>
+  </si>
+  <si>
+    <t>14023.2</t>
   </si>
   <si>
     <t>140.2</t>
@@ -458,7 +458,13 @@
     <t>31일</t>
   </si>
   <si>
-    <t>0.0</t>
+    <t>579.3</t>
+  </si>
+  <si>
+    <t>14602.5</t>
+  </si>
+  <si>
+    <t>146.0</t>
   </si>
 </sst>
 </file>
@@ -1372,13 +1378,13 @@
         <v>148</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>148</v>
+        <v>86</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
